--- a/resources/templates/heyman/roro_invoice_packing.xlsx
+++ b/resources/templates/heyman/roro_invoice_packing.xlsx
@@ -46,11 +46,11 @@
   </si>
   <si>
     <t>HEYMAN LTD.,
-63, Seonghyeon-ro, Ilsandong-gu, Goyang-si, 
-Gyeonggi-do, Republic of Korea
+#513, THE PARK 365, 50 Seonyudong1-ro,
+Yeongdeungpo-gu, Seoul, Korea
 TEL:82-505-355-9977 
 FAX:82-505-366-9977
-EMAIL : man99777@naver.com</t>
+EMAIL : heyman99888@gmail.com</t>
   </si>
   <si>
     <r>

--- a/resources/templates/heyman/roro_invoice_packing.xlsx
+++ b/resources/templates/heyman/roro_invoice_packing.xlsx
@@ -48,7 +48,7 @@
     <t>HEYMAN LTD.,
 #513, THE PARK 365, 50 Seonyudong1-ro,
 Yeongdeungpo-gu, Seoul, Korea
-TEL:82-505-355-9977 
+TEL:82-10-9009-9977 
 FAX:82-505-366-9977
 EMAIL : heyman99888@gmail.com</t>
   </si>
